--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2024_los_lagos.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -417,7 +417,7 @@
         <v>6.64668319142605</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>2.898807466996156</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -471,7 +471,7 @@
         <v>4.388456195618495</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         <v>3.639488636446608</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -525,7 +525,7 @@
         <v>4.79170695312825</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -552,13 +552,13 @@
         <v>4.284643583746828</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chiloé</t>
+          <t>Chiloe</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -579,13 +579,13 @@
         <v>2.034401945645392</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chiloé</t>
+          <t>Chiloe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -606,13 +606,13 @@
         <v>3.176489587044617</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chiloé</t>
+          <t>Chiloe</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -633,13 +633,13 @@
         <v>2.662492824141682</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="C11">
-        <v>349410.69</v>
+        <v>323246.94</v>
       </c>
       <c r="D11">
-        <v>342704.66</v>
+        <v>315322.72</v>
       </c>
       <c r="E11">
-        <v>6706.030000000028</v>
+        <v>7924.22000000003</v>
       </c>
       <c r="F11">
-        <v>1.956795685241053</v>
+        <v>2.513050756380641</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -675,45 +675,126 @@
         </is>
       </c>
       <c r="C12">
-        <v>510816.28</v>
+        <v>465962.75</v>
       </c>
       <c r="D12">
-        <v>492226.19</v>
+        <v>448337.81</v>
       </c>
       <c r="E12">
-        <v>18590.09000000003</v>
+        <v>17624.94</v>
       </c>
       <c r="F12">
-        <v>3.776737276007203</v>
+        <v>3.931174129614456</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>394492.59</v>
+      </c>
+      <c r="D13">
+        <v>381861.84</v>
+      </c>
+      <c r="E13">
+        <v>12630.75</v>
+      </c>
+      <c r="F13">
+        <v>3.307675362377127</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Llanquihue</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>349410.69</v>
+      </c>
+      <c r="D14">
+        <v>342704.66</v>
+      </c>
+      <c r="E14">
+        <v>6706.030000000028</v>
+      </c>
+      <c r="F14">
+        <v>1.956795685241053</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>510816.28</v>
+      </c>
+      <c r="D15">
+        <v>492226.19</v>
+      </c>
+      <c r="E15">
+        <v>18590.09000000003</v>
+      </c>
+      <c r="F15">
+        <v>3.776737276007203</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C13">
+      <c r="C16">
         <v>430151.56</v>
       </c>
-      <c r="D13">
+      <c r="D16">
         <v>417681.09</v>
       </c>
-      <c r="E13">
+      <c r="E16">
         <v>12470.46999999997</v>
       </c>
-      <c r="F13">
+      <c r="F16">
         <v>2.985643903582025</v>
       </c>
-      <c r="G13">
+      <c r="G16">
         <v>1</v>
       </c>
     </row>
@@ -742,7 +823,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chiloé</t>
+          <t>Chiloe</t>
         </is>
       </c>
       <c r="B2">
@@ -786,7 +867,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -814,7 +895,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chiloé</t>
+          <t>Chiloe</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -832,7 +913,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chiloé</t>
+          <t>Chiloe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -850,7 +931,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chiloé</t>
+          <t>Chiloe</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1024,6 +1105,60 @@
         <v>329125.09</v>
       </c>
       <c r="D13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>344231.88</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>381861.84</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>394492.59</v>
+      </c>
+      <c r="D16" t="b">
         <v>1</v>
       </c>
     </row>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2024_los_lagos.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:10</t>
+    <t xml:space="preserve">2026-07-30 18:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -86,13 +86,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_ingr_mean_a_2024_los_lagos.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingreso de la población en edad de trabajar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Los Lagos</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -905,23 +911,23 @@
         <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -1001,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
@@ -1012,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>317973.06</v>
@@ -1023,7 +1029,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>354870.44</v>
@@ -1034,7 +1040,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>364318.84</v>
@@ -1045,7 +1051,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>376639.38</v>
@@ -1056,7 +1062,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>417681.09</v>
@@ -1067,7 +1073,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>430151.56</v>
@@ -1078,7 +1084,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>313704.12</v>
@@ -1089,7 +1095,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>344980.62</v>
@@ -1100,7 +1106,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>359761.81</v>
@@ -1111,7 +1117,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>265048.88</v>
@@ -1122,7 +1128,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>315288.78</v>
@@ -1133,7 +1139,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>329125.09</v>
@@ -1144,7 +1150,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>344231.88</v>
@@ -1155,7 +1161,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>381861.84</v>
@@ -1166,7 +1172,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>394492.59</v>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2024_los_lagos.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">Osorno</t>
   </si>
   <si>
-    <t xml:space="preserve">Chiloe</t>
+    <t xml:space="preserve">Chiloé</t>
   </si>
   <si>
     <t xml:space="preserve">Promedio Regional</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 18:07</t>
+    <t xml:space="preserve">2026-08-19 15:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2024_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 15:18</t>
+    <t xml:space="preserve">2026-09-07 11:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
